--- a/existing_workbooks/CA - Jul 26.xlsx
+++ b/existing_workbooks/CA - Jul 26.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhair\OneDrive\Documents\Aadeshwar\G1\Jul 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7285e1571d1ef5af/Documents/Aadeshwar/G1/Jul 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE586AB7-9517-48B1-9395-F719044EC3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{FE586AB7-9517-48B1-9395-F719044EC3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34FBD694-8CA2-4811-97AE-9AFDD783ACD7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8C80EEB7-5523-4769-9289-00E302BD76D7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{8C80EEB7-5523-4769-9289-00E302BD76D7}"/>
   </bookViews>
   <sheets>
-    <sheet name="21.6.26" sheetId="1" r:id="rId1"/>
-    <sheet name="22.6.26" sheetId="2" r:id="rId2"/>
-    <sheet name="23.6.26" sheetId="3" r:id="rId3"/>
-    <sheet name="24.6.26" sheetId="4" r:id="rId4"/>
-    <sheet name="25.6.26" sheetId="5" r:id="rId5"/>
-    <sheet name="26.6.26" sheetId="6" r:id="rId6"/>
+    <sheet name="21.06.2026" sheetId="1" r:id="rId1"/>
+    <sheet name="22.06.2026" sheetId="2" r:id="rId2"/>
+    <sheet name="23.06.2026" sheetId="3" r:id="rId3"/>
+    <sheet name="24.06.2026" sheetId="4" r:id="rId4"/>
+    <sheet name="25.06.2026" sheetId="5" r:id="rId5"/>
+    <sheet name="26.06.2026" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -782,6 +782,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
